--- a/financial_advisor_forms/007_retirement_planning_questionnaire--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/007_retirement_planning_questionnaire--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>account_type_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What type of account do you have</t>
+          <t>Account Type 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>calculator_account</t>
+          <t>calculator_account_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Do you have a retirement calculator account</t>
+          <t>Calculator Account 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>trust_account</t>
+          <t>trust_account_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Do you have a retirement account in a trust</t>
+          <t>Trust Account 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>account_type_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>account_type_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>account_type_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>account_type_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>calculator_account_choices</t>
+          <t>calculator_account_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>calculator_account_choices</t>
+          <t>calculator_account_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>trust_account_choices</t>
+          <t>trust_account_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>trust_account_choices</t>
+          <t>trust_account_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
